--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426611</v>
+        <v>113426629</v>
       </c>
       <c r="B2" t="n">
-        <v>56781</v>
+        <v>94108</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296248</v>
+        <v>296269</v>
       </c>
       <c r="R2" t="n">
-        <v>6530032</v>
+        <v>6530070</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426628</v>
+        <v>113426610</v>
       </c>
       <c r="B3" t="n">
-        <v>94092</v>
+        <v>56765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296306</v>
+        <v>296217</v>
       </c>
       <c r="R3" t="n">
-        <v>6530234</v>
+        <v>6529973</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426626</v>
+        <v>113426611</v>
       </c>
       <c r="B4" t="n">
-        <v>91290</v>
+        <v>56781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296284</v>
+        <v>296248</v>
       </c>
       <c r="R4" t="n">
-        <v>6530076</v>
+        <v>6530032</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426610</v>
+        <v>113426612</v>
       </c>
       <c r="B5" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296217</v>
+        <v>296274</v>
       </c>
       <c r="R5" t="n">
-        <v>6529973</v>
+        <v>6530070</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426629</v>
+        <v>113426619</v>
       </c>
       <c r="B6" t="n">
-        <v>94092</v>
+        <v>56781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296269</v>
+        <v>296319</v>
       </c>
       <c r="R6" t="n">
-        <v>6530070</v>
+        <v>6530155</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1174,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426620</v>
+        <v>113426628</v>
       </c>
       <c r="B7" t="n">
-        <v>56781</v>
+        <v>94108</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296231</v>
+        <v>296306</v>
       </c>
       <c r="R7" t="n">
-        <v>6530043</v>
+        <v>6530234</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1276,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426612</v>
+        <v>113426626</v>
       </c>
       <c r="B8" t="n">
-        <v>56781</v>
+        <v>91306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296274</v>
+        <v>296284</v>
       </c>
       <c r="R8" t="n">
-        <v>6530070</v>
+        <v>6530076</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426619</v>
+        <v>113426620</v>
       </c>
       <c r="B9" t="n">
         <v>56781</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296319</v>
+        <v>296231</v>
       </c>
       <c r="R9" t="n">
-        <v>6530155</v>
+        <v>6530043</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426629</v>
+        <v>113426619</v>
       </c>
       <c r="B2" t="n">
-        <v>94108</v>
+        <v>56781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296269</v>
+        <v>296319</v>
       </c>
       <c r="R2" t="n">
-        <v>6530070</v>
+        <v>6530155</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426610</v>
+        <v>113426626</v>
       </c>
       <c r="B3" t="n">
-        <v>56765</v>
+        <v>91306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296217</v>
+        <v>296284</v>
       </c>
       <c r="R3" t="n">
-        <v>6529973</v>
+        <v>6530076</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426611</v>
+        <v>113426628</v>
       </c>
       <c r="B4" t="n">
-        <v>56781</v>
+        <v>94108</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296248</v>
+        <v>296306</v>
       </c>
       <c r="R4" t="n">
-        <v>6530032</v>
+        <v>6530234</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426612</v>
+        <v>113426620</v>
       </c>
       <c r="B5" t="n">
         <v>56781</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296274</v>
+        <v>296231</v>
       </c>
       <c r="R5" t="n">
-        <v>6530070</v>
+        <v>6530043</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426619</v>
+        <v>113426611</v>
       </c>
       <c r="B6" t="n">
         <v>56781</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296319</v>
+        <v>296248</v>
       </c>
       <c r="R6" t="n">
-        <v>6530155</v>
+        <v>6530032</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426628</v>
+        <v>113426629</v>
       </c>
       <c r="B7" t="n">
         <v>94108</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296306</v>
+        <v>296269</v>
       </c>
       <c r="R7" t="n">
-        <v>6530234</v>
+        <v>6530070</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426626</v>
+        <v>113426612</v>
       </c>
       <c r="B8" t="n">
-        <v>91306</v>
+        <v>56781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296284</v>
+        <v>296274</v>
       </c>
       <c r="R8" t="n">
-        <v>6530076</v>
+        <v>6530070</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426620</v>
+        <v>113426610</v>
       </c>
       <c r="B9" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296231</v>
+        <v>296217</v>
       </c>
       <c r="R9" t="n">
-        <v>6530043</v>
+        <v>6529973</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426619</v>
+        <v>113426612</v>
       </c>
       <c r="B2" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296319</v>
+        <v>296274</v>
       </c>
       <c r="R2" t="n">
-        <v>6530155</v>
+        <v>6530070</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426626</v>
+        <v>113426620</v>
       </c>
       <c r="B3" t="n">
-        <v>91306</v>
+        <v>56782</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296284</v>
+        <v>296231</v>
       </c>
       <c r="R3" t="n">
-        <v>6530076</v>
+        <v>6530043</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426628</v>
+        <v>113426629</v>
       </c>
       <c r="B4" t="n">
-        <v>94108</v>
+        <v>94120</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296306</v>
+        <v>296269</v>
       </c>
       <c r="R4" t="n">
-        <v>6530234</v>
+        <v>6530070</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426620</v>
+        <v>113426628</v>
       </c>
       <c r="B5" t="n">
-        <v>56781</v>
+        <v>94120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296231</v>
+        <v>296306</v>
       </c>
       <c r="R5" t="n">
-        <v>6530043</v>
+        <v>6530234</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426611</v>
+        <v>113426626</v>
       </c>
       <c r="B6" t="n">
-        <v>56781</v>
+        <v>91318</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296248</v>
+        <v>296284</v>
       </c>
       <c r="R6" t="n">
-        <v>6530032</v>
+        <v>6530076</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426629</v>
+        <v>113426611</v>
       </c>
       <c r="B7" t="n">
-        <v>94108</v>
+        <v>56782</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296269</v>
+        <v>296248</v>
       </c>
       <c r="R7" t="n">
-        <v>6530070</v>
+        <v>6530032</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1281,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426612</v>
+        <v>113426619</v>
       </c>
       <c r="B8" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296274</v>
+        <v>296319</v>
       </c>
       <c r="R8" t="n">
-        <v>6530070</v>
+        <v>6530155</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1417,7 +1417,7 @@
         <v>113426610</v>
       </c>
       <c r="B9" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426612</v>
+        <v>113426620</v>
       </c>
       <c r="B2" t="n">
         <v>56782</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296274</v>
+        <v>296231</v>
       </c>
       <c r="R2" t="n">
-        <v>6530070</v>
+        <v>6530043</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426620</v>
+        <v>113426611</v>
       </c>
       <c r="B3" t="n">
         <v>56782</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296231</v>
+        <v>296248</v>
       </c>
       <c r="R3" t="n">
-        <v>6530043</v>
+        <v>6530032</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426629</v>
+        <v>113426610</v>
       </c>
       <c r="B4" t="n">
-        <v>94120</v>
+        <v>56766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296269</v>
+        <v>296217</v>
       </c>
       <c r="R4" t="n">
-        <v>6530070</v>
+        <v>6529973</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426628</v>
+        <v>113426629</v>
       </c>
       <c r="B5" t="n">
         <v>94120</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296306</v>
+        <v>296269</v>
       </c>
       <c r="R5" t="n">
-        <v>6530234</v>
+        <v>6530070</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426626</v>
+        <v>113426612</v>
       </c>
       <c r="B6" t="n">
-        <v>91318</v>
+        <v>56782</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296284</v>
+        <v>296274</v>
       </c>
       <c r="R6" t="n">
-        <v>6530076</v>
+        <v>6530070</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426611</v>
+        <v>113426619</v>
       </c>
       <c r="B7" t="n">
         <v>56782</v>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296248</v>
+        <v>296319</v>
       </c>
       <c r="R7" t="n">
-        <v>6530032</v>
+        <v>6530155</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426619</v>
+        <v>113426628</v>
       </c>
       <c r="B8" t="n">
-        <v>56782</v>
+        <v>94120</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1324,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296319</v>
+        <v>296306</v>
       </c>
       <c r="R8" t="n">
-        <v>6530155</v>
+        <v>6530234</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1383,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426610</v>
+        <v>113426626</v>
       </c>
       <c r="B9" t="n">
-        <v>56766</v>
+        <v>91318</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296217</v>
+        <v>296284</v>
       </c>
       <c r="R9" t="n">
-        <v>6529973</v>
+        <v>6530076</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426610</v>
+        <v>113426629</v>
       </c>
       <c r="B4" t="n">
-        <v>56766</v>
+        <v>94120</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296217</v>
+        <v>296269</v>
       </c>
       <c r="R4" t="n">
-        <v>6529973</v>
+        <v>6530070</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426629</v>
+        <v>113426610</v>
       </c>
       <c r="B5" t="n">
-        <v>94120</v>
+        <v>56766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296269</v>
+        <v>296217</v>
       </c>
       <c r="R5" t="n">
-        <v>6530070</v>
+        <v>6529973</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426620</v>
+        <v>113426628</v>
       </c>
       <c r="B2" t="n">
-        <v>56782</v>
+        <v>94142</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296231</v>
+        <v>296306</v>
       </c>
       <c r="R2" t="n">
-        <v>6530043</v>
+        <v>6530234</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426611</v>
+        <v>113426612</v>
       </c>
       <c r="B3" t="n">
         <v>56782</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296248</v>
+        <v>296274</v>
       </c>
       <c r="R3" t="n">
-        <v>6530032</v>
+        <v>6530070</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426629</v>
+        <v>113426626</v>
       </c>
       <c r="B4" t="n">
-        <v>94120</v>
+        <v>91340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296269</v>
+        <v>296284</v>
       </c>
       <c r="R4" t="n">
-        <v>6530070</v>
+        <v>6530076</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426612</v>
+        <v>113426611</v>
       </c>
       <c r="B6" t="n">
         <v>56782</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296274</v>
+        <v>296248</v>
       </c>
       <c r="R6" t="n">
-        <v>6530070</v>
+        <v>6530032</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426628</v>
+        <v>113426629</v>
       </c>
       <c r="B8" t="n">
-        <v>94120</v>
+        <v>94142</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296306</v>
+        <v>296269</v>
       </c>
       <c r="R8" t="n">
-        <v>6530234</v>
+        <v>6530070</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426626</v>
+        <v>113426620</v>
       </c>
       <c r="B9" t="n">
-        <v>91318</v>
+        <v>56782</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296284</v>
+        <v>296231</v>
       </c>
       <c r="R9" t="n">
-        <v>6530076</v>
+        <v>6530043</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426628</v>
+        <v>113426626</v>
       </c>
       <c r="B2" t="n">
-        <v>94142</v>
+        <v>91344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296306</v>
+        <v>296284</v>
       </c>
       <c r="R2" t="n">
-        <v>6530234</v>
+        <v>6530076</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426612</v>
+        <v>113426619</v>
       </c>
       <c r="B3" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296274</v>
+        <v>296319</v>
       </c>
       <c r="R3" t="n">
-        <v>6530070</v>
+        <v>6530155</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426626</v>
+        <v>113426611</v>
       </c>
       <c r="B4" t="n">
-        <v>91340</v>
+        <v>56785</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296284</v>
+        <v>296248</v>
       </c>
       <c r="R4" t="n">
-        <v>6530076</v>
+        <v>6530032</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426610</v>
+        <v>113426629</v>
       </c>
       <c r="B5" t="n">
-        <v>56766</v>
+        <v>94146</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296217</v>
+        <v>296269</v>
       </c>
       <c r="R5" t="n">
-        <v>6529973</v>
+        <v>6530070</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426611</v>
+        <v>113426620</v>
       </c>
       <c r="B6" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296248</v>
+        <v>296231</v>
       </c>
       <c r="R6" t="n">
-        <v>6530032</v>
+        <v>6530043</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426619</v>
+        <v>113426612</v>
       </c>
       <c r="B7" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296319</v>
+        <v>296274</v>
       </c>
       <c r="R7" t="n">
-        <v>6530155</v>
+        <v>6530070</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426629</v>
+        <v>113426628</v>
       </c>
       <c r="B8" t="n">
-        <v>94142</v>
+        <v>94146</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296269</v>
+        <v>296306</v>
       </c>
       <c r="R8" t="n">
-        <v>6530070</v>
+        <v>6530234</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426620</v>
+        <v>113426610</v>
       </c>
       <c r="B9" t="n">
-        <v>56782</v>
+        <v>56769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296231</v>
+        <v>296217</v>
       </c>
       <c r="R9" t="n">
-        <v>6530043</v>
+        <v>6529973</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426626</v>
+        <v>113426619</v>
       </c>
       <c r="B2" t="n">
-        <v>91344</v>
+        <v>56785</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296284</v>
+        <v>296319</v>
       </c>
       <c r="R2" t="n">
-        <v>6530076</v>
+        <v>6530155</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426619</v>
+        <v>113426628</v>
       </c>
       <c r="B3" t="n">
-        <v>56785</v>
+        <v>94146</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296319</v>
+        <v>296306</v>
       </c>
       <c r="R3" t="n">
-        <v>6530155</v>
+        <v>6530234</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426611</v>
+        <v>113426620</v>
       </c>
       <c r="B4" t="n">
         <v>56785</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296248</v>
+        <v>296231</v>
       </c>
       <c r="R4" t="n">
-        <v>6530032</v>
+        <v>6530043</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426629</v>
+        <v>113426611</v>
       </c>
       <c r="B5" t="n">
-        <v>94146</v>
+        <v>56785</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296269</v>
+        <v>296248</v>
       </c>
       <c r="R5" t="n">
-        <v>6530070</v>
+        <v>6530032</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426620</v>
+        <v>113426629</v>
       </c>
       <c r="B6" t="n">
-        <v>56785</v>
+        <v>94146</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296231</v>
+        <v>296269</v>
       </c>
       <c r="R6" t="n">
-        <v>6530043</v>
+        <v>6530070</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1174,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426612</v>
+        <v>113426610</v>
       </c>
       <c r="B7" t="n">
-        <v>56785</v>
+        <v>56769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,16 +1216,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296274</v>
+        <v>296217</v>
       </c>
       <c r="R7" t="n">
-        <v>6530070</v>
+        <v>6529973</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426628</v>
+        <v>113426626</v>
       </c>
       <c r="B8" t="n">
-        <v>94146</v>
+        <v>91344</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296306</v>
+        <v>296284</v>
       </c>
       <c r="R8" t="n">
-        <v>6530234</v>
+        <v>6530076</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426610</v>
+        <v>113426612</v>
       </c>
       <c r="B9" t="n">
-        <v>56769</v>
+        <v>56785</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296217</v>
+        <v>296274</v>
       </c>
       <c r="R9" t="n">
-        <v>6529973</v>
+        <v>6530070</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426619</v>
+        <v>113426628</v>
       </c>
       <c r="B2" t="n">
-        <v>56785</v>
+        <v>94152</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296319</v>
+        <v>296306</v>
       </c>
       <c r="R2" t="n">
-        <v>6530155</v>
+        <v>6530234</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426628</v>
+        <v>113426612</v>
       </c>
       <c r="B3" t="n">
-        <v>94146</v>
+        <v>56789</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296306</v>
+        <v>296274</v>
       </c>
       <c r="R3" t="n">
-        <v>6530234</v>
+        <v>6530070</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426620</v>
+        <v>113426626</v>
       </c>
       <c r="B4" t="n">
-        <v>56785</v>
+        <v>91350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296231</v>
+        <v>296284</v>
       </c>
       <c r="R4" t="n">
-        <v>6530043</v>
+        <v>6530076</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426611</v>
+        <v>113426620</v>
       </c>
       <c r="B5" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296248</v>
+        <v>296231</v>
       </c>
       <c r="R5" t="n">
-        <v>6530032</v>
+        <v>6530043</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426629</v>
+        <v>113426611</v>
       </c>
       <c r="B6" t="n">
-        <v>94146</v>
+        <v>56789</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296269</v>
+        <v>296248</v>
       </c>
       <c r="R6" t="n">
-        <v>6530070</v>
+        <v>6530032</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1174,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426610</v>
+        <v>113426619</v>
       </c>
       <c r="B7" t="n">
-        <v>56769</v>
+        <v>56789</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,16 +1221,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296217</v>
+        <v>296319</v>
       </c>
       <c r="R7" t="n">
-        <v>6529973</v>
+        <v>6530155</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426626</v>
+        <v>113426610</v>
       </c>
       <c r="B8" t="n">
-        <v>91344</v>
+        <v>56773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1324,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296284</v>
+        <v>296217</v>
       </c>
       <c r="R8" t="n">
-        <v>6530076</v>
+        <v>6529973</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426612</v>
+        <v>113426629</v>
       </c>
       <c r="B9" t="n">
-        <v>56785</v>
+        <v>94152</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1431,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,7 +1459,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296274</v>
+        <v>296269</v>
       </c>
       <c r="R9" t="n">
         <v>6530070</v>
@@ -1490,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426628</v>
+        <v>113426626</v>
       </c>
       <c r="B2" t="n">
-        <v>94152</v>
+        <v>91350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296306</v>
+        <v>296284</v>
       </c>
       <c r="R2" t="n">
-        <v>6530234</v>
+        <v>6530076</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426612</v>
+        <v>113426610</v>
       </c>
       <c r="B3" t="n">
-        <v>56789</v>
+        <v>56773</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296274</v>
+        <v>296217</v>
       </c>
       <c r="R3" t="n">
-        <v>6530070</v>
+        <v>6529973</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426626</v>
+        <v>113426612</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>56789</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296284</v>
+        <v>296274</v>
       </c>
       <c r="R4" t="n">
-        <v>6530076</v>
+        <v>6530070</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426620</v>
+        <v>113426619</v>
       </c>
       <c r="B5" t="n">
         <v>56789</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296231</v>
+        <v>296319</v>
       </c>
       <c r="R5" t="n">
-        <v>6530043</v>
+        <v>6530155</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426619</v>
+        <v>113426628</v>
       </c>
       <c r="B7" t="n">
-        <v>56789</v>
+        <v>94152</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296319</v>
+        <v>296306</v>
       </c>
       <c r="R7" t="n">
-        <v>6530155</v>
+        <v>6530234</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426610</v>
+        <v>113426629</v>
       </c>
       <c r="B8" t="n">
-        <v>56773</v>
+        <v>94152</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1324,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296217</v>
+        <v>296269</v>
       </c>
       <c r="R8" t="n">
-        <v>6529973</v>
+        <v>6530070</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426629</v>
+        <v>113426620</v>
       </c>
       <c r="B9" t="n">
-        <v>94152</v>
+        <v>56789</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296269</v>
+        <v>296231</v>
       </c>
       <c r="R9" t="n">
-        <v>6530070</v>
+        <v>6530043</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426626</v>
+        <v>113426629</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>94159</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296284</v>
+        <v>296269</v>
       </c>
       <c r="R2" t="n">
-        <v>6530076</v>
+        <v>6530070</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426610</v>
+        <v>113426619</v>
       </c>
       <c r="B3" t="n">
-        <v>56773</v>
+        <v>56796</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296217</v>
+        <v>296319</v>
       </c>
       <c r="R3" t="n">
-        <v>6529973</v>
+        <v>6530155</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426612</v>
+        <v>113426628</v>
       </c>
       <c r="B4" t="n">
-        <v>56789</v>
+        <v>94159</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296274</v>
+        <v>296306</v>
       </c>
       <c r="R4" t="n">
-        <v>6530070</v>
+        <v>6530234</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426619</v>
+        <v>113426620</v>
       </c>
       <c r="B5" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296319</v>
+        <v>296231</v>
       </c>
       <c r="R5" t="n">
-        <v>6530155</v>
+        <v>6530043</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426611</v>
+        <v>113426612</v>
       </c>
       <c r="B6" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296248</v>
+        <v>296274</v>
       </c>
       <c r="R6" t="n">
-        <v>6530032</v>
+        <v>6530070</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1210,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426628</v>
+        <v>113426611</v>
       </c>
       <c r="B7" t="n">
-        <v>94152</v>
+        <v>56796</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296306</v>
+        <v>296248</v>
       </c>
       <c r="R7" t="n">
-        <v>6530234</v>
+        <v>6530032</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1286,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426629</v>
+        <v>113426626</v>
       </c>
       <c r="B8" t="n">
-        <v>94152</v>
+        <v>91357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296269</v>
+        <v>296284</v>
       </c>
       <c r="R8" t="n">
-        <v>6530070</v>
+        <v>6530076</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426620</v>
+        <v>113426610</v>
       </c>
       <c r="B9" t="n">
-        <v>56789</v>
+        <v>56780</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296231</v>
+        <v>296217</v>
       </c>
       <c r="R9" t="n">
-        <v>6530043</v>
+        <v>6529973</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426620</v>
+        <v>113426626</v>
       </c>
       <c r="B5" t="n">
-        <v>56796</v>
+        <v>91357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296231</v>
+        <v>296284</v>
       </c>
       <c r="R5" t="n">
-        <v>6530043</v>
+        <v>6530076</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426612</v>
+        <v>113426620</v>
       </c>
       <c r="B6" t="n">
         <v>56796</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296274</v>
+        <v>296231</v>
       </c>
       <c r="R6" t="n">
-        <v>6530070</v>
+        <v>6530043</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426611</v>
+        <v>113426612</v>
       </c>
       <c r="B7" t="n">
         <v>56796</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296248</v>
+        <v>296274</v>
       </c>
       <c r="R7" t="n">
-        <v>6530032</v>
+        <v>6530070</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426626</v>
+        <v>113426611</v>
       </c>
       <c r="B8" t="n">
-        <v>91357</v>
+        <v>56796</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296284</v>
+        <v>296248</v>
       </c>
       <c r="R8" t="n">
-        <v>6530076</v>
+        <v>6530032</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426629</v>
+        <v>113426626</v>
       </c>
       <c r="B2" t="n">
-        <v>94159</v>
+        <v>91362</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296269</v>
+        <v>296284</v>
       </c>
       <c r="R2" t="n">
-        <v>6530070</v>
+        <v>6530076</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426619</v>
+        <v>113426620</v>
       </c>
       <c r="B3" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296319</v>
+        <v>296231</v>
       </c>
       <c r="R3" t="n">
-        <v>6530155</v>
+        <v>6530043</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426628</v>
+        <v>113426629</v>
       </c>
       <c r="B4" t="n">
-        <v>94159</v>
+        <v>94164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296306</v>
+        <v>296269</v>
       </c>
       <c r="R4" t="n">
-        <v>6530234</v>
+        <v>6530070</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426626</v>
+        <v>113426628</v>
       </c>
       <c r="B5" t="n">
-        <v>91357</v>
+        <v>94164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296284</v>
+        <v>296306</v>
       </c>
       <c r="R5" t="n">
-        <v>6530076</v>
+        <v>6530234</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426620</v>
+        <v>113426619</v>
       </c>
       <c r="B6" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296231</v>
+        <v>296319</v>
       </c>
       <c r="R6" t="n">
-        <v>6530043</v>
+        <v>6530155</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,7 +1203,7 @@
         <v>113426612</v>
       </c>
       <c r="B7" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426611</v>
+        <v>113426610</v>
       </c>
       <c r="B8" t="n">
-        <v>56796</v>
+        <v>56782</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,16 +1323,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296248</v>
+        <v>296217</v>
       </c>
       <c r="R8" t="n">
-        <v>6530032</v>
+        <v>6529973</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426610</v>
+        <v>113426611</v>
       </c>
       <c r="B9" t="n">
-        <v>56780</v>
+        <v>56798</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296217</v>
+        <v>296248</v>
       </c>
       <c r="R9" t="n">
-        <v>6529973</v>
+        <v>6530032</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426626</v>
+        <v>113426628</v>
       </c>
       <c r="B2" t="n">
-        <v>91362</v>
+        <v>94192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296284</v>
+        <v>296306</v>
       </c>
       <c r="R2" t="n">
-        <v>6530076</v>
+        <v>6530234</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426620</v>
+        <v>113426611</v>
       </c>
       <c r="B3" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296231</v>
+        <v>296248</v>
       </c>
       <c r="R3" t="n">
-        <v>6530043</v>
+        <v>6530032</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426629</v>
+        <v>113426619</v>
       </c>
       <c r="B4" t="n">
-        <v>94164</v>
+        <v>56826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296269</v>
+        <v>296319</v>
       </c>
       <c r="R4" t="n">
-        <v>6530070</v>
+        <v>6530155</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426628</v>
+        <v>113426610</v>
       </c>
       <c r="B5" t="n">
-        <v>94164</v>
+        <v>56810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296306</v>
+        <v>296217</v>
       </c>
       <c r="R5" t="n">
-        <v>6530234</v>
+        <v>6529973</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1067,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426619</v>
+        <v>113426629</v>
       </c>
       <c r="B6" t="n">
-        <v>56798</v>
+        <v>94192</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296319</v>
+        <v>296269</v>
       </c>
       <c r="R6" t="n">
-        <v>6530155</v>
+        <v>6530070</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1169,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426612</v>
+        <v>113426626</v>
       </c>
       <c r="B7" t="n">
-        <v>56798</v>
+        <v>91390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296274</v>
+        <v>296284</v>
       </c>
       <c r="R7" t="n">
-        <v>6530070</v>
+        <v>6530076</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426610</v>
+        <v>113426612</v>
       </c>
       <c r="B8" t="n">
-        <v>56782</v>
+        <v>56826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,16 +1323,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296217</v>
+        <v>296274</v>
       </c>
       <c r="R8" t="n">
-        <v>6529973</v>
+        <v>6530070</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426611</v>
+        <v>113426620</v>
       </c>
       <c r="B9" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296248</v>
+        <v>296231</v>
       </c>
       <c r="R9" t="n">
-        <v>6530032</v>
+        <v>6530043</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426628</v>
+        <v>113426610</v>
       </c>
       <c r="B2" t="n">
-        <v>94192</v>
+        <v>56810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296306</v>
+        <v>296217</v>
       </c>
       <c r="R2" t="n">
-        <v>6530234</v>
+        <v>6529973</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426611</v>
+        <v>113426619</v>
       </c>
       <c r="B3" t="n">
         <v>56826</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296248</v>
+        <v>296319</v>
       </c>
       <c r="R3" t="n">
-        <v>6530032</v>
+        <v>6530155</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426619</v>
+        <v>113426620</v>
       </c>
       <c r="B4" t="n">
         <v>56826</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296319</v>
+        <v>296231</v>
       </c>
       <c r="R4" t="n">
-        <v>6530155</v>
+        <v>6530043</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426610</v>
+        <v>113426611</v>
       </c>
       <c r="B5" t="n">
-        <v>56810</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,16 +1012,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296217</v>
+        <v>296248</v>
       </c>
       <c r="R5" t="n">
-        <v>6529973</v>
+        <v>6530032</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426629</v>
+        <v>113426628</v>
       </c>
       <c r="B6" t="n">
         <v>94192</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296269</v>
+        <v>296306</v>
       </c>
       <c r="R6" t="n">
-        <v>6530070</v>
+        <v>6530234</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426626</v>
+        <v>113426629</v>
       </c>
       <c r="B7" t="n">
-        <v>91390</v>
+        <v>94192</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296284</v>
+        <v>296269</v>
       </c>
       <c r="R7" t="n">
-        <v>6530076</v>
+        <v>6530070</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1276,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426620</v>
+        <v>113426626</v>
       </c>
       <c r="B9" t="n">
-        <v>56826</v>
+        <v>91390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296231</v>
+        <v>296284</v>
       </c>
       <c r="R9" t="n">
-        <v>6530043</v>
+        <v>6530076</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426610</v>
+        <v>113426626</v>
       </c>
       <c r="B2" t="n">
-        <v>56810</v>
+        <v>91394</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296217</v>
+        <v>296284</v>
       </c>
       <c r="R2" t="n">
-        <v>6529973</v>
+        <v>6530076</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426619</v>
+        <v>113426610</v>
       </c>
       <c r="B3" t="n">
-        <v>56826</v>
+        <v>56810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296319</v>
+        <v>296217</v>
       </c>
       <c r="R3" t="n">
-        <v>6530155</v>
+        <v>6529973</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426620</v>
+        <v>113426628</v>
       </c>
       <c r="B4" t="n">
-        <v>56826</v>
+        <v>94196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296231</v>
+        <v>296306</v>
       </c>
       <c r="R4" t="n">
-        <v>6530043</v>
+        <v>6530234</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426611</v>
+        <v>113426629</v>
       </c>
       <c r="B5" t="n">
-        <v>56826</v>
+        <v>94196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296248</v>
+        <v>296269</v>
       </c>
       <c r="R5" t="n">
-        <v>6530032</v>
+        <v>6530070</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426628</v>
+        <v>113426611</v>
       </c>
       <c r="B6" t="n">
-        <v>94192</v>
+        <v>56826</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296306</v>
+        <v>296248</v>
       </c>
       <c r="R6" t="n">
-        <v>6530234</v>
+        <v>6530032</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1179,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426629</v>
+        <v>113426619</v>
       </c>
       <c r="B7" t="n">
-        <v>94192</v>
+        <v>56826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296269</v>
+        <v>296319</v>
       </c>
       <c r="R7" t="n">
-        <v>6530070</v>
+        <v>6530155</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1281,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426626</v>
+        <v>113426620</v>
       </c>
       <c r="B9" t="n">
-        <v>91390</v>
+        <v>56826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296284</v>
+        <v>296231</v>
       </c>
       <c r="R9" t="n">
-        <v>6530076</v>
+        <v>6530043</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13950-2023 artfynd.xlsx
+++ b/artfynd/A 13950-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
